--- a/アプリケーション企画実習/テーブル詳細一覧.xlsx
+++ b/アプリケーション企画実習/テーブル詳細一覧.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s0101\OneDrive\デスクトップ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.10.253\Studio1\企画制作実習_2026_05\B_久曜上野小橋タイガース\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B990F0BA-53B3-45FE-884D-1BCECD0D48FB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E20868-836B-4620-9322-52CC5E07E1B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14685" windowHeight="11985" xr2:uid="{ACCA7A6E-E5CB-4EDE-B27B-2B20B6E310F2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12015" xr2:uid="{ACCA7A6E-E5CB-4EDE-B27B-2B20B6E310F2}"/>
   </bookViews>
   <sheets>
-    <sheet name="猫" sheetId="1" r:id="rId1"/>
+    <sheet name="猫" sheetId="8" r:id="rId1"/>
     <sheet name="犬" sheetId="2" r:id="rId2"/>
     <sheet name="里親" sheetId="3" r:id="rId3"/>
     <sheet name="イベント" sheetId="6" r:id="rId4"/>
@@ -23,7 +23,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">犬!$A$2:$L$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">猫!$A$2:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">団体!$A$2:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">猫!$A$2:$M$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">里親!$A$2:$E$32</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="527">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -75,9 +76,6 @@
     <t>こむぎ</t>
   </si>
   <si>
-    <t>くぅ</t>
-  </si>
-  <si>
     <t>みけ</t>
   </si>
   <si>
@@ -357,16 +355,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>去勢</t>
-    <rPh sb="0" eb="1">
-      <t>キョ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>ゼイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>混合ワクチン</t>
     <rPh sb="0" eb="2">
       <t>コンゴウ</t>
@@ -886,16 +874,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>団体名</t>
-    <rPh sb="0" eb="2">
-      <t>ダンタイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>イベント(event)テーブル</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1084,13 +1062,1268 @@
   </si>
   <si>
     <t>ノルウェージャンフォレストキャット</t>
+  </si>
+  <si>
+    <t>柴犬</t>
+    <rPh sb="0" eb="2">
+      <t>シバイヌ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雑種</t>
+    <rPh sb="0" eb="2">
+      <t>ザッシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チワワ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トイプードル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポメラニアン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マルチーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ミニチュアダックスフンド</t>
+  </si>
+  <si>
+    <t>シーズー</t>
+  </si>
+  <si>
+    <t>ゴールデンレトリーバー</t>
+  </si>
+  <si>
+    <t>ラブラドールレトリーバー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>からし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鼻炎を起こしやすいため、定期的な動物病院への通院が必要</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>食べムラがあるため、ウェットフードを活用するなど工夫が必要</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>捕獲器</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ケージへの誘導</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>負傷動物として保護</t>
+  </si>
+  <si>
+    <t>抱っこ・直接保護</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山道</t>
+    <rPh sb="0" eb="2">
+      <t>サンドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高齢者宅</t>
+    <rPh sb="0" eb="3">
+      <t>コウレイシャ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>公園</t>
+    <rPh sb="0" eb="2">
+      <t>コウエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空き家</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>駐車場</t>
+    <rPh sb="0" eb="3">
+      <t>チュウシャジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空き地</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>神戸市市民宅</t>
+    <rPh sb="0" eb="3">
+      <t>コウベシ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シミン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>多頭飼育崩壊による保護</t>
+    <rPh sb="0" eb="2">
+      <t>タトウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シイク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ホウカイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クレートに入るのが少し苦手</t>
+    <rPh sb="9" eb="10">
+      <t>スコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保護状況</t>
+    <rPh sb="0" eb="4">
+      <t>ホゴジョウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保護中</t>
+    <rPh sb="0" eb="3">
+      <t>ホゴチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>譲渡済</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡</t>
+    <rPh sb="0" eb="2">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有</t>
+    <rPh sb="0" eb="1">
+      <t>アリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無</t>
+    <rPh sb="0" eb="1">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>団体名</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>代表者名</t>
+    <rPh sb="0" eb="3">
+      <t>ダイヒョウシャ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受入上限数</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウゲン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メモ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>茶の間犬猫暮らし</t>
+    <rPh sb="0" eb="1">
+      <t>チャ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イヌネコ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>静岡県島田市中溝3-4-15</t>
+  </si>
+  <si>
+    <t>0544-05-2187</t>
+  </si>
+  <si>
+    <t>kawaguchi_shinji@example.ne.jp</t>
+  </si>
+  <si>
+    <t>宮崎 聡</t>
+  </si>
+  <si>
+    <t>あわじ動物の足跡</t>
+    <rPh sb="3" eb="5">
+      <t>ドウブツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>アシアト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>兵庫県洲本市本町4-3-9</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0797-55-5027</t>
+  </si>
+  <si>
+    <t>shinohara_masako@example.com</t>
+  </si>
+  <si>
+    <t>三矢 友明</t>
+  </si>
+  <si>
+    <t>ハナノキ愛の家</t>
+    <rPh sb="4" eb="5">
+      <t>アイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>イエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>愛知県名古屋市天白区一つ山1-5-21</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0586-93-2705</t>
+  </si>
+  <si>
+    <t>megumi_matsunaga@example.net</t>
+  </si>
+  <si>
+    <t>奥原 知明</t>
+  </si>
+  <si>
+    <t>秋桜動物愛護団体</t>
+    <rPh sb="0" eb="1">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>サクラ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ドウブツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>アイゴ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ダンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>神奈川県川崎市宮前区東有馬1-1-13</t>
+  </si>
+  <si>
+    <t>0465-22-7968</t>
+  </si>
+  <si>
+    <t>keijikiryuu@example.ne.jp</t>
+  </si>
+  <si>
+    <t>吉岡 昇悟</t>
+  </si>
+  <si>
+    <t>夢の通ひ路動物へ</t>
+    <rPh sb="0" eb="1">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>トオル</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大阪府大阪市住之江区北加賀屋1-2-22</t>
+  </si>
+  <si>
+    <t>06-6727-5168</t>
+  </si>
+  <si>
+    <t>ryouta_sano@example.com</t>
+  </si>
+  <si>
+    <t>高橋 聖也</t>
+  </si>
+  <si>
+    <t>富山ひかりの犬クラブ</t>
+    <rPh sb="0" eb="2">
+      <t>トヤマ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>イヌ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>富山県富山市二口町3-2-10</t>
+  </si>
+  <si>
+    <t>0766-74-7901</t>
+  </si>
+  <si>
+    <t>hashimotoakira@example.jp</t>
+  </si>
+  <si>
+    <t>井上 聖子</t>
+  </si>
+  <si>
+    <t>SHIMANEKKO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>島根県出雲市塩冶神前2-4-12</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0853-65-9862</t>
+  </si>
+  <si>
+    <t>matsumoto49@example.jp</t>
+  </si>
+  <si>
+    <t>野々村 渉</t>
+  </si>
+  <si>
+    <t>あまあまアニマルズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>兵庫県尼崎市東難波町1-2-9</t>
+  </si>
+  <si>
+    <t>0796-76-0520</t>
+  </si>
+  <si>
+    <t>aoi_amano@example.jp</t>
+  </si>
+  <si>
+    <t>塚越 尭</t>
+  </si>
+  <si>
+    <t>いぬねこのL太郎</t>
+    <rPh sb="6" eb="8">
+      <t>タロウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東京都杉並区成田東1-2-6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03-7777-5891</t>
+  </si>
+  <si>
+    <t>takashi_matsumoto@example.ne.jp</t>
+  </si>
+  <si>
+    <t>大浦 まどか</t>
+  </si>
+  <si>
+    <t>しっぽをゆく</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大阪府東大阪市中小阪1-3-3</t>
+  </si>
+  <si>
+    <t>06-7224-1368</t>
+  </si>
+  <si>
+    <t>kyouko_noda@example.ne.jp</t>
+  </si>
+  <si>
+    <t>白川 みほ</t>
+  </si>
+  <si>
+    <t>性別　</t>
+    <rPh sb="0" eb="2">
+      <t>セイベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>役職</t>
+    <rPh sb="0" eb="2">
+      <t>ヤクショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログインID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>板倉 祥子</t>
+  </si>
+  <si>
+    <t>神奈川県横浜市鶴見区鶴見中央2-2-10</t>
+  </si>
+  <si>
+    <t>0463-06-4117</t>
+  </si>
+  <si>
+    <t>shoukoitakura@example.co.jp</t>
+  </si>
+  <si>
+    <t>1976年06月15日</t>
+  </si>
+  <si>
+    <t>常勤スタッフ</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Shouko0615</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DFyg9m8B</t>
+  </si>
+  <si>
+    <t>池田 正顕</t>
+  </si>
+  <si>
+    <t>大阪府大阪市中央区南船場1-4-1107</t>
+  </si>
+  <si>
+    <t>06-7854-4393</t>
+  </si>
+  <si>
+    <t>ikedamasaaki@example.com</t>
+  </si>
+  <si>
+    <t>1958年06月25日</t>
+  </si>
+  <si>
+    <t>施設長･シェルター長(権限有)</t>
+    <rPh sb="0" eb="2">
+      <t>シセツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>アリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Masaki0625</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pMUyjG8V</t>
+  </si>
+  <si>
+    <t>鈴木 洋輔</t>
+  </si>
+  <si>
+    <t>福岡県福岡市中央区薬院1-1-808</t>
+  </si>
+  <si>
+    <t>092-095-6764</t>
+  </si>
+  <si>
+    <t>suzukiyousuke@example.com</t>
+  </si>
+  <si>
+    <t>1995年01月04日</t>
+  </si>
+  <si>
+    <t>ボランティア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>staff00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>r5XDAz3J</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>笹野 江里子</t>
+  </si>
+  <si>
+    <t>宮城県仙台市若林区大和町2-1-21プリオーレ114</t>
+  </si>
+  <si>
+    <t>0220-97-7139</t>
+  </si>
+  <si>
+    <t>erikosasano@example.net</t>
+  </si>
+  <si>
+    <t>1978年11月06日</t>
+  </si>
+  <si>
+    <t>Eriko1106</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>z3LrJfg4</t>
+  </si>
+  <si>
+    <t>田中 明子</t>
+  </si>
+  <si>
+    <t>千葉県松戸市新松戸1-1-5</t>
+  </si>
+  <si>
+    <t>0438-51-5169</t>
+  </si>
+  <si>
+    <t>tanakaakiko@example.net</t>
+  </si>
+  <si>
+    <t>1983年12月07日</t>
+  </si>
+  <si>
+    <t>Kiko1207</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>s96KYQhV</t>
+  </si>
+  <si>
+    <t>篠田 大樹</t>
+  </si>
+  <si>
+    <t>埼玉県さいたま市中央区本町東3-3-19</t>
+  </si>
+  <si>
+    <t>04-3656-2912</t>
+  </si>
+  <si>
+    <t>taikishinoda@example.jp</t>
+  </si>
+  <si>
+    <t>1960年10月04日</t>
+  </si>
+  <si>
+    <t>staff00</t>
+  </si>
+  <si>
+    <t>r5XDAz3J</t>
+  </si>
+  <si>
+    <t>梅本 裕貴</t>
+  </si>
+  <si>
+    <t>愛媛県松山市山越4-3-6</t>
+  </si>
+  <si>
+    <t>0896-76-5654</t>
+  </si>
+  <si>
+    <t>umemoto_918@example.co.jp</t>
+  </si>
+  <si>
+    <t>1957年03月22日</t>
+  </si>
+  <si>
+    <t>Yuuki0322</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>yLc42C6J</t>
+  </si>
+  <si>
+    <t>田中 義高</t>
+  </si>
+  <si>
+    <t>大阪府大阪市東住吉区今川4-2-8</t>
+  </si>
+  <si>
+    <t>06-6745-7647</t>
+  </si>
+  <si>
+    <t>tanaka_yoshitaka@example.ne.jp</t>
+  </si>
+  <si>
+    <t>1958年01月06日</t>
+  </si>
+  <si>
+    <t>山本 真也</t>
+  </si>
+  <si>
+    <t>東京都大田区西糀谷4-2-8</t>
+  </si>
+  <si>
+    <t>03-3474-7156</t>
+  </si>
+  <si>
+    <t>yamamoto_shinya@example.co.jp</t>
+  </si>
+  <si>
+    <t>1990年09月16日</t>
+  </si>
+  <si>
+    <t>宮里 清美</t>
+  </si>
+  <si>
+    <t>宮崎県宮崎市太田2-3-5</t>
+  </si>
+  <si>
+    <t>0987-75-6230</t>
+  </si>
+  <si>
+    <t>miyazato1121@example.ne.jp</t>
+  </si>
+  <si>
+    <t>2000年04月29日</t>
+  </si>
+  <si>
+    <t>勝又 真里</t>
+  </si>
+  <si>
+    <t>東京都杉並区荻窪2-5-17</t>
+  </si>
+  <si>
+    <t>03-2554-8306</t>
+  </si>
+  <si>
+    <t>katsumata18@example.co.jp</t>
+  </si>
+  <si>
+    <t>1951年08月05日</t>
+  </si>
+  <si>
+    <t>副代表(権限有)</t>
+    <rPh sb="0" eb="3">
+      <t>フクダイヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mari0805</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>iS4F9MTb</t>
+  </si>
+  <si>
+    <t>塩見 幸代</t>
+  </si>
+  <si>
+    <t>東京都千代田区麹町2-1-1102</t>
+  </si>
+  <si>
+    <t>03-8761-3250</t>
+  </si>
+  <si>
+    <t>shiomi_yukiyo@example.com</t>
+  </si>
+  <si>
+    <t>1970年11月23日</t>
+  </si>
+  <si>
+    <t>今橋 貴</t>
+  </si>
+  <si>
+    <t>福岡県福岡市博多区博多駅南2-5-603メロディーハイム410</t>
+  </si>
+  <si>
+    <t>0948-95-9097</t>
+  </si>
+  <si>
+    <t>imahashi_1230@example.net</t>
+  </si>
+  <si>
+    <t>1999年06月23日</t>
+  </si>
+  <si>
+    <t>三浦 ゆうこ</t>
+  </si>
+  <si>
+    <t>大阪府大阪市福島区玉川3-3-10</t>
+  </si>
+  <si>
+    <t>06-3773-3770</t>
+  </si>
+  <si>
+    <t>yuukomiura@example.net</t>
+  </si>
+  <si>
+    <t>1953年07月15日</t>
+  </si>
+  <si>
+    <t>事務局長(権限有)</t>
+    <rPh sb="0" eb="2">
+      <t>ジム</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョクチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Yuuko0715</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>N6dCHwr7</t>
+  </si>
+  <si>
+    <t>江口 花織</t>
+  </si>
+  <si>
+    <t>神奈川県川崎市高津区末長2-2-7</t>
+  </si>
+  <si>
+    <t>045-061-6489</t>
+  </si>
+  <si>
+    <t>kaori_eguchi@example.co.jp</t>
+  </si>
+  <si>
+    <t>1993年12月01日</t>
+  </si>
+  <si>
+    <t>安井 斐子</t>
+  </si>
+  <si>
+    <t>広島県広島市西区高須台3-5-17</t>
+  </si>
+  <si>
+    <t>0845-11-8917</t>
+  </si>
+  <si>
+    <t>ayakoyasui@example.co.jp</t>
+  </si>
+  <si>
+    <t>1960年04月08日</t>
+  </si>
+  <si>
+    <t>宮岡 英樹</t>
+  </si>
+  <si>
+    <t>東京都港区虎ノ門2-2-3</t>
+  </si>
+  <si>
+    <t>03-5296-7654</t>
+  </si>
+  <si>
+    <t>miyaokahideki@example.com</t>
+  </si>
+  <si>
+    <t>1986年07月15日</t>
+  </si>
+  <si>
+    <t>橋口 優</t>
+  </si>
+  <si>
+    <t>東京都中央区銀座3-2-8</t>
+  </si>
+  <si>
+    <t>03-0457-1602</t>
+  </si>
+  <si>
+    <t>hashiguchi_yuu@example.net</t>
+  </si>
+  <si>
+    <t>1973年12月02日</t>
+  </si>
+  <si>
+    <t>黛 サトコ</t>
+  </si>
+  <si>
+    <t>山口県宇部市亀浦3-1-7</t>
+  </si>
+  <si>
+    <t>083-215-8684</t>
+  </si>
+  <si>
+    <t>mayuzumisatoko@example.com</t>
+  </si>
+  <si>
+    <t>1945年10月16日</t>
+  </si>
+  <si>
+    <t>代表理事(権限有)</t>
+    <rPh sb="0" eb="2">
+      <t>ダイヒョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>リジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Satoko1016</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kR33Q6ib</t>
+  </si>
+  <si>
+    <t>大山 ももこ</t>
+  </si>
+  <si>
+    <t>東京都豊島区東池袋3-2-904</t>
+  </si>
+  <si>
+    <t>03-6006-9992</t>
+  </si>
+  <si>
+    <t>oyama_76@example.jp</t>
+  </si>
+  <si>
+    <t>2002年01月20日</t>
+  </si>
+  <si>
+    <t>Momoko0120</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sR4JR3nT</t>
+  </si>
+  <si>
+    <t>飼い主の経済的理由により飼育困難に</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヌシ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ケイザイテキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シイク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コンナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ケージでの受け渡し</t>
+    <rPh sb="5" eb="6">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ワタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保健所収容数をオーバーしたため、当団体で保護</t>
+  </si>
+  <si>
+    <t>保健所</t>
+    <rPh sb="0" eb="3">
+      <t>ホケンジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>住宅地</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウタクチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商業施設周辺</t>
+  </si>
+  <si>
+    <t>右前足を負傷していたため病院にて治療、継続して動物病院への通院が必要</t>
+    <rPh sb="0" eb="1">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>マエアシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>フショウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ビョウイン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>チリョウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ケイゾク</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>ドウブツビョウイン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ツウイン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>交差点付近</t>
+    <rPh sb="0" eb="3">
+      <t>コウサテン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>フキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>駅周辺</t>
+    <rPh sb="0" eb="3">
+      <t>エキシュウヘン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>河川敷</t>
+  </si>
+  <si>
+    <t>神戸市市民宅</t>
+    <rPh sb="0" eb="2">
+      <t>コウベ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シミン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>飼い主病気入院のため、飼育困難に</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヌシ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ビョウキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニュウイン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シイク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コンナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フードを手に置いて口元まで持っていくと食べてくれる</t>
+    <rPh sb="4" eb="5">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>クチモト</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残飯を食べていた模様。ガリガリに瘦せている</t>
+    <rPh sb="0" eb="2">
+      <t>ザンパン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>モヨウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TNR活動中に保護、子猫のため当団体で継続し保護</t>
+    <rPh sb="3" eb="6">
+      <t>カツドウチュウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ホゴ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コネコ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>トウダンタイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ケイゾク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ホゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保護主からの委託で保護</t>
+    <rPh sb="0" eb="2">
+      <t>ホゴ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヌシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イタク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>少し怖がりな性格</t>
+    <rPh sb="0" eb="1">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コワ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保健所収容数をオーバーしたため、当団体で保護</t>
+    <rPh sb="0" eb="3">
+      <t>ホケンジョ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュウヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ダンタイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ホゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目の状態が悪く、目薬投薬中。継続した点眼が必要</t>
+    <rPh sb="0" eb="1">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ワル</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>メグスリ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>トウヤクチュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ケイゾク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>テンガン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保護時ケガをしていたため、病院にて治療、程なく死亡</t>
+    <rPh sb="0" eb="2">
+      <t>ホゴ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ビョウイン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>チリョウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ホド</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保護中</t>
+    <rPh sb="0" eb="2">
+      <t>ホゴ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その他事項</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>健康に関する特記事項</t>
+    <rPh sb="0" eb="2">
+      <t>ケンコウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トッキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>避妊</t>
+    <rPh sb="0" eb="2">
+      <t>ヒニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1111,6 +2344,14 @@
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF6C6C6C"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1229,7 +2470,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1260,6 +2501,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1575,689 +2828,1438 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19188B67-D093-41EC-B767-91E29C71723A}">
-  <dimension ref="A1:K47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C26491E-A294-4B0E-A3A9-4CAFD301D00E}">
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="3" max="3" width="35.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="70.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="56.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="I2" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L2" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C3" t="s">
-        <v>277</v>
-      </c>
-      <c r="G3" s="8">
+        <v>274</v>
+      </c>
+      <c r="E3" t="s">
+        <v>304</v>
+      </c>
+      <c r="F3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G3" t="s">
+        <v>312</v>
+      </c>
+      <c r="H3" s="8">
         <v>45816</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="I3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C4" t="s">
-        <v>278</v>
-      </c>
-      <c r="G4" s="8">
+        <v>275</v>
+      </c>
+      <c r="E4" t="s">
+        <v>507</v>
+      </c>
+      <c r="F4" t="s">
+        <v>299</v>
+      </c>
+      <c r="G4" t="s">
+        <v>313</v>
+      </c>
+      <c r="H4" s="8">
         <v>45502</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="I4" t="s">
+        <v>315</v>
+      </c>
+      <c r="J4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C5" t="s">
-        <v>279</v>
-      </c>
-      <c r="G5" s="8">
+        <v>276</v>
+      </c>
+      <c r="E5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F5" t="s">
+        <v>301</v>
+      </c>
+      <c r="G5" t="s">
+        <v>523</v>
+      </c>
+      <c r="H5" s="8">
         <v>45325</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="I5" t="s">
+        <v>315</v>
+      </c>
+      <c r="J5" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s">
-        <v>280</v>
-      </c>
-      <c r="G6" s="8">
+        <v>277</v>
+      </c>
+      <c r="E6" t="s">
+        <v>302</v>
+      </c>
+      <c r="F6" t="s">
+        <v>300</v>
+      </c>
+      <c r="G6" t="s">
+        <v>314</v>
+      </c>
+      <c r="H6" s="8">
         <v>45977</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="I6" t="s">
+        <v>315</v>
+      </c>
+      <c r="J6" t="s">
+        <v>316</v>
+      </c>
+      <c r="L6" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>295</v>
       </c>
       <c r="B7" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C7" t="s">
-        <v>281</v>
-      </c>
-      <c r="G7" s="8">
-        <v>44952</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="E7" t="s">
+        <v>306</v>
+      </c>
+      <c r="F7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G7" t="s">
+        <v>312</v>
+      </c>
+      <c r="H7" s="8">
+        <v>45110</v>
+      </c>
+      <c r="I7" t="s">
+        <v>315</v>
+      </c>
+      <c r="J7" t="s">
+        <v>315</v>
+      </c>
+      <c r="L7" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C8" t="s">
         <v>278</v>
       </c>
-      <c r="G8" s="8">
-        <v>45110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="E8" t="s">
+        <v>308</v>
+      </c>
+      <c r="F8" t="s">
+        <v>504</v>
+      </c>
+      <c r="G8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H8" s="8">
+        <v>44952</v>
+      </c>
+      <c r="I8" t="s">
+        <v>315</v>
+      </c>
+      <c r="J8" t="s">
+        <v>315</v>
+      </c>
+      <c r="M8" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C9" t="s">
-        <v>278</v>
-      </c>
-      <c r="G9" s="8">
+        <v>275</v>
+      </c>
+      <c r="E9" t="s">
+        <v>304</v>
+      </c>
+      <c r="F9" t="s">
+        <v>301</v>
+      </c>
+      <c r="G9" t="s">
+        <v>312</v>
+      </c>
+      <c r="H9" s="8">
         <v>45143</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="I9" t="s">
+        <v>315</v>
+      </c>
+      <c r="J9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C10" t="s">
+        <v>279</v>
+      </c>
+      <c r="E10" t="s">
+        <v>507</v>
+      </c>
+      <c r="F10" t="s">
+        <v>301</v>
+      </c>
+      <c r="G10" t="s">
+        <v>312</v>
+      </c>
+      <c r="H10" s="8">
+        <v>45689</v>
+      </c>
+      <c r="I10" t="s">
+        <v>315</v>
+      </c>
+      <c r="J10" t="s">
+        <v>315</v>
+      </c>
+      <c r="L10" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C11" t="s">
+        <v>280</v>
+      </c>
+      <c r="E11" t="s">
+        <v>506</v>
+      </c>
+      <c r="F11" t="s">
+        <v>504</v>
+      </c>
+      <c r="G11" t="s">
+        <v>312</v>
+      </c>
+      <c r="H11" s="8">
+        <v>44945</v>
+      </c>
+      <c r="I11" t="s">
+        <v>315</v>
+      </c>
+      <c r="J11" t="s">
+        <v>315</v>
+      </c>
+      <c r="M11" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C12" t="s">
+        <v>281</v>
+      </c>
+      <c r="E12" t="s">
+        <v>302</v>
+      </c>
+      <c r="F12" t="s">
+        <v>298</v>
+      </c>
+      <c r="G12" t="s">
+        <v>312</v>
+      </c>
+      <c r="H12" s="8">
+        <v>46160</v>
+      </c>
+      <c r="I12" t="s">
+        <v>315</v>
+      </c>
+      <c r="J12" t="s">
+        <v>315</v>
+      </c>
+      <c r="M12" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>268</v>
+      </c>
+      <c r="C13" t="s">
         <v>282</v>
       </c>
-      <c r="G10" s="8">
-        <v>45689</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>272</v>
-      </c>
-      <c r="C11" t="s">
-        <v>283</v>
-      </c>
-      <c r="G11" s="8">
-        <v>44945</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" t="s">
-        <v>272</v>
-      </c>
-      <c r="C12" t="s">
-        <v>284</v>
-      </c>
-      <c r="G12" s="8">
-        <v>46374</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" t="s">
-        <v>271</v>
-      </c>
-      <c r="C13" t="s">
-        <v>285</v>
-      </c>
-      <c r="G13" s="8">
+      <c r="E13" t="s">
+        <v>507</v>
+      </c>
+      <c r="F13" t="s">
+        <v>504</v>
+      </c>
+      <c r="G13" t="s">
+        <v>312</v>
+      </c>
+      <c r="H13" s="8">
         <v>45392</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="I13" t="s">
+        <v>315</v>
+      </c>
+      <c r="J13" t="s">
+        <v>315</v>
+      </c>
+      <c r="M13" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C14" t="s">
-        <v>286</v>
-      </c>
-      <c r="G14" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+        <v>283</v>
+      </c>
+      <c r="E14" t="s">
+        <v>304</v>
+      </c>
+      <c r="F14" t="s">
+        <v>301</v>
+      </c>
+      <c r="G14" t="s">
+        <v>312</v>
+      </c>
+      <c r="H14" s="8">
+        <v>45438</v>
+      </c>
+      <c r="I14" t="s">
+        <v>315</v>
+      </c>
+      <c r="J14" t="s">
+        <v>315</v>
+      </c>
+      <c r="M14" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C15" t="s">
-        <v>282</v>
-      </c>
-      <c r="G15" s="8">
+        <v>279</v>
+      </c>
+      <c r="E15" t="s">
+        <v>305</v>
+      </c>
+      <c r="F15" t="s">
+        <v>301</v>
+      </c>
+      <c r="G15" t="s">
+        <v>312</v>
+      </c>
+      <c r="H15" s="8">
         <v>45753</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="I15" t="s">
+        <v>315</v>
+      </c>
+      <c r="J15" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C16" t="s">
-        <v>278</v>
-      </c>
-      <c r="G16" s="8">
+        <v>275</v>
+      </c>
+      <c r="E16" t="s">
+        <v>512</v>
+      </c>
+      <c r="F16" t="s">
+        <v>299</v>
+      </c>
+      <c r="G16" t="s">
+        <v>312</v>
+      </c>
+      <c r="H16" s="8">
         <v>45315</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I16" t="s">
+        <v>315</v>
+      </c>
+      <c r="J16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C17" t="s">
-        <v>283</v>
-      </c>
-      <c r="G17" s="8">
+        <v>280</v>
+      </c>
+      <c r="E17" t="s">
+        <v>304</v>
+      </c>
+      <c r="F17" t="s">
+        <v>301</v>
+      </c>
+      <c r="G17" t="s">
+        <v>312</v>
+      </c>
+      <c r="H17" s="8">
         <v>46055</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I17" t="s">
+        <v>316</v>
+      </c>
+      <c r="J17" t="s">
+        <v>316</v>
+      </c>
+      <c r="L17" t="s">
+        <v>516</v>
+      </c>
+      <c r="M17" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C18" t="s">
-        <v>277</v>
-      </c>
-      <c r="G18" s="8">
-        <v>46336</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+        <v>274</v>
+      </c>
+      <c r="E18" t="s">
+        <v>306</v>
+      </c>
+      <c r="F18" t="s">
+        <v>300</v>
+      </c>
+      <c r="G18" t="s">
+        <v>312</v>
+      </c>
+      <c r="H18" s="8">
+        <v>46032</v>
+      </c>
+      <c r="I18" t="s">
+        <v>315</v>
+      </c>
+      <c r="J18" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C19" t="s">
-        <v>282</v>
-      </c>
-      <c r="G19" s="8">
+        <v>279</v>
+      </c>
+      <c r="E19" t="s">
+        <v>302</v>
+      </c>
+      <c r="F19" t="s">
+        <v>298</v>
+      </c>
+      <c r="G19" t="s">
+        <v>312</v>
+      </c>
+      <c r="H19" s="8">
         <v>45757</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I19" t="s">
+        <v>315</v>
+      </c>
+      <c r="J19" t="s">
+        <v>315</v>
+      </c>
+      <c r="M19" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C20" t="s">
-        <v>281</v>
-      </c>
-      <c r="G20" s="8">
+        <v>278</v>
+      </c>
+      <c r="E20" t="s">
+        <v>513</v>
+      </c>
+      <c r="F20" t="s">
+        <v>504</v>
+      </c>
+      <c r="G20" t="s">
+        <v>312</v>
+      </c>
+      <c r="H20" s="8">
         <v>46159</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I20" t="s">
+        <v>316</v>
+      </c>
+      <c r="J20" t="s">
+        <v>316</v>
+      </c>
+      <c r="M20" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C21" t="s">
-        <v>278</v>
-      </c>
-      <c r="G21" s="8">
+        <v>275</v>
+      </c>
+      <c r="E21" t="s">
+        <v>507</v>
+      </c>
+      <c r="F21" t="s">
+        <v>301</v>
+      </c>
+      <c r="G21" t="s">
+        <v>312</v>
+      </c>
+      <c r="H21" s="8">
         <v>44946</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I21" t="s">
+        <v>315</v>
+      </c>
+      <c r="J21" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C22" t="s">
-        <v>283</v>
-      </c>
-      <c r="G22" s="8">
+        <v>280</v>
+      </c>
+      <c r="E22" t="s">
+        <v>512</v>
+      </c>
+      <c r="F22" t="s">
+        <v>299</v>
+      </c>
+      <c r="G22" t="s">
+        <v>312</v>
+      </c>
+      <c r="H22" s="8">
         <v>45764</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I22" t="s">
+        <v>315</v>
+      </c>
+      <c r="J22" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C23" t="s">
-        <v>287</v>
-      </c>
-      <c r="G23" s="8">
+        <v>284</v>
+      </c>
+      <c r="E23" t="s">
+        <v>308</v>
+      </c>
+      <c r="F23" t="s">
+        <v>504</v>
+      </c>
+      <c r="G23" t="s">
+        <v>312</v>
+      </c>
+      <c r="H23" s="8">
         <v>46012</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I23" t="s">
+        <v>315</v>
+      </c>
+      <c r="J23" t="s">
+        <v>315</v>
+      </c>
+      <c r="M23" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C24" t="s">
-        <v>281</v>
-      </c>
-      <c r="G24" s="8">
+        <v>278</v>
+      </c>
+      <c r="E24" t="s">
+        <v>307</v>
+      </c>
+      <c r="F24" t="s">
+        <v>301</v>
+      </c>
+      <c r="G24" t="s">
+        <v>312</v>
+      </c>
+      <c r="H24" s="8">
         <v>45035</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I24" t="s">
+        <v>315</v>
+      </c>
+      <c r="J24" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C25" t="s">
-        <v>283</v>
-      </c>
-      <c r="G25" s="8">
+        <v>280</v>
+      </c>
+      <c r="E25" t="s">
+        <v>508</v>
+      </c>
+      <c r="F25" t="s">
+        <v>301</v>
+      </c>
+      <c r="G25" t="s">
+        <v>312</v>
+      </c>
+      <c r="H25" s="8">
         <v>46001</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I25" t="s">
+        <v>315</v>
+      </c>
+      <c r="J25" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C26" t="s">
-        <v>284</v>
-      </c>
-      <c r="G26" s="8">
+        <v>281</v>
+      </c>
+      <c r="E26" t="s">
+        <v>308</v>
+      </c>
+      <c r="F26" t="s">
+        <v>504</v>
+      </c>
+      <c r="G26" t="s">
+        <v>312</v>
+      </c>
+      <c r="H26" s="8">
         <v>45413</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I26" t="s">
+        <v>315</v>
+      </c>
+      <c r="J26" t="s">
+        <v>315</v>
+      </c>
+      <c r="M26" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C27" t="s">
+        <v>279</v>
+      </c>
+      <c r="E27" t="s">
+        <v>304</v>
+      </c>
+      <c r="F27" t="s">
+        <v>301</v>
+      </c>
+      <c r="G27" t="s">
+        <v>312</v>
+      </c>
+      <c r="H27" s="8">
+        <v>45220</v>
+      </c>
+      <c r="I27" t="s">
+        <v>315</v>
+      </c>
+      <c r="J27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A28" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" t="s">
+        <v>269</v>
+      </c>
+      <c r="C28" t="s">
         <v>282</v>
       </c>
-      <c r="G27" s="8">
-        <v>45220</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A28" s="3" t="s">
+      <c r="E28" t="s">
+        <v>308</v>
+      </c>
+      <c r="F28" t="s">
+        <v>504</v>
+      </c>
+      <c r="G28" t="s">
+        <v>312</v>
+      </c>
+      <c r="H28" s="8">
+        <v>46231</v>
+      </c>
+      <c r="I28" t="s">
+        <v>316</v>
+      </c>
+      <c r="J28" t="s">
+        <v>316</v>
+      </c>
+      <c r="M28" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A29" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B28" t="s">
-        <v>272</v>
-      </c>
-      <c r="C28" t="s">
-        <v>285</v>
-      </c>
-      <c r="G28" s="8">
-        <v>46260</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A29" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="B29" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C29" t="s">
-        <v>280</v>
-      </c>
-      <c r="G29" s="8">
+        <v>277</v>
+      </c>
+      <c r="E29" t="s">
+        <v>307</v>
+      </c>
+      <c r="F29" t="s">
+        <v>299</v>
+      </c>
+      <c r="G29" t="s">
+        <v>312</v>
+      </c>
+      <c r="H29" s="8">
         <v>44930</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I29" t="s">
+        <v>315</v>
+      </c>
+      <c r="J29" t="s">
+        <v>315</v>
+      </c>
+      <c r="M29" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C30" t="s">
+        <v>279</v>
+      </c>
+      <c r="E30" t="s">
+        <v>511</v>
+      </c>
+      <c r="F30" t="s">
+        <v>301</v>
+      </c>
+      <c r="G30" t="s">
+        <v>312</v>
+      </c>
+      <c r="H30" s="8">
+        <v>44945</v>
+      </c>
+      <c r="I30" t="s">
+        <v>315</v>
+      </c>
+      <c r="J30" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" t="s">
+        <v>268</v>
+      </c>
+      <c r="C31" t="s">
         <v>282</v>
       </c>
-      <c r="G30" s="8">
-        <v>44945</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" t="s">
-        <v>271</v>
-      </c>
-      <c r="C31" t="s">
-        <v>285</v>
-      </c>
-      <c r="G31" s="8">
+      <c r="E31" t="s">
+        <v>513</v>
+      </c>
+      <c r="F31" t="s">
+        <v>504</v>
+      </c>
+      <c r="G31" t="s">
+        <v>312</v>
+      </c>
+      <c r="H31" s="8">
         <v>46231</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I31" t="s">
+        <v>316</v>
+      </c>
+      <c r="J31" t="s">
+        <v>316</v>
+      </c>
+      <c r="M31" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A32" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C32" t="s">
-        <v>277</v>
-      </c>
-      <c r="G32" s="8">
+        <v>274</v>
+      </c>
+      <c r="E32" t="s">
+        <v>512</v>
+      </c>
+      <c r="F32" t="s">
+        <v>299</v>
+      </c>
+      <c r="G32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H32" s="8">
         <v>45785</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I32" t="s">
+        <v>315</v>
+      </c>
+      <c r="J32" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C33" t="s">
-        <v>282</v>
-      </c>
-      <c r="G33" s="8">
+        <v>279</v>
+      </c>
+      <c r="E33" t="s">
+        <v>507</v>
+      </c>
+      <c r="F33" t="s">
+        <v>301</v>
+      </c>
+      <c r="G33" t="s">
+        <v>312</v>
+      </c>
+      <c r="H33" s="8">
         <v>45289</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I33" t="s">
+        <v>315</v>
+      </c>
+      <c r="J33" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C34" t="s">
-        <v>281</v>
-      </c>
-      <c r="G34" s="8">
+        <v>278</v>
+      </c>
+      <c r="E34" t="s">
+        <v>306</v>
+      </c>
+      <c r="F34" t="s">
+        <v>300</v>
+      </c>
+      <c r="G34" t="s">
+        <v>312</v>
+      </c>
+      <c r="H34" s="8">
         <v>46191</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I34" t="s">
+        <v>315</v>
+      </c>
+      <c r="J34" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A35" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C35" t="s">
-        <v>284</v>
-      </c>
-      <c r="G35" s="8">
+        <v>281</v>
+      </c>
+      <c r="E35" t="s">
+        <v>512</v>
+      </c>
+      <c r="F35" t="s">
+        <v>299</v>
+      </c>
+      <c r="G35" t="s">
+        <v>312</v>
+      </c>
+      <c r="H35" s="8">
         <v>45697</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I35" t="s">
+        <v>315</v>
+      </c>
+      <c r="J35" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A36" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C36" t="s">
-        <v>282</v>
-      </c>
-      <c r="G36" s="8">
+        <v>279</v>
+      </c>
+      <c r="E36" t="s">
+        <v>302</v>
+      </c>
+      <c r="F36" t="s">
+        <v>298</v>
+      </c>
+      <c r="G36" t="s">
+        <v>312</v>
+      </c>
+      <c r="H36" s="8">
         <v>45252</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I36" t="s">
+        <v>315</v>
+      </c>
+      <c r="J36" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A37" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C37" t="s">
-        <v>277</v>
-      </c>
-      <c r="G37" s="8">
+        <v>274</v>
+      </c>
+      <c r="E37" t="s">
+        <v>507</v>
+      </c>
+      <c r="F37" t="s">
+        <v>301</v>
+      </c>
+      <c r="G37" t="s">
+        <v>312</v>
+      </c>
+      <c r="H37" s="8">
         <v>45493</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I37" t="s">
+        <v>315</v>
+      </c>
+      <c r="J37" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A38" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B38" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C38" t="s">
-        <v>284</v>
-      </c>
-      <c r="G38" s="8">
+        <v>281</v>
+      </c>
+      <c r="E38" t="s">
+        <v>512</v>
+      </c>
+      <c r="F38" t="s">
+        <v>301</v>
+      </c>
+      <c r="G38" t="s">
+        <v>312</v>
+      </c>
+      <c r="H38" s="8">
         <v>46019</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I38" t="s">
+        <v>315</v>
+      </c>
+      <c r="J38" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C39" t="s">
+        <v>275</v>
+      </c>
+      <c r="E39" t="s">
+        <v>511</v>
+      </c>
+      <c r="F39" t="s">
+        <v>301</v>
+      </c>
+      <c r="G39" t="s">
+        <v>312</v>
+      </c>
+      <c r="H39" s="8">
+        <v>45555</v>
+      </c>
+      <c r="I39" t="s">
+        <v>315</v>
+      </c>
+      <c r="J39" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" t="s">
+        <v>268</v>
+      </c>
+      <c r="C40" t="s">
+        <v>284</v>
+      </c>
+      <c r="E40" t="s">
+        <v>308</v>
+      </c>
+      <c r="F40" t="s">
+        <v>504</v>
+      </c>
+      <c r="G40" t="s">
+        <v>312</v>
+      </c>
+      <c r="H40" s="8">
+        <v>45798</v>
+      </c>
+      <c r="I40" t="s">
+        <v>316</v>
+      </c>
+      <c r="J40" t="s">
+        <v>315</v>
+      </c>
+      <c r="M40" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" t="s">
+        <v>269</v>
+      </c>
+      <c r="C41" t="s">
+        <v>280</v>
+      </c>
+      <c r="E41" t="s">
+        <v>510</v>
+      </c>
+      <c r="F41" t="s">
+        <v>300</v>
+      </c>
+      <c r="G41" t="s">
+        <v>312</v>
+      </c>
+      <c r="H41" s="8">
+        <v>45595</v>
+      </c>
+      <c r="I41" t="s">
+        <v>315</v>
+      </c>
+      <c r="J41" t="s">
+        <v>315</v>
+      </c>
+      <c r="L41" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" t="s">
+        <v>269</v>
+      </c>
+      <c r="C42" t="s">
+        <v>281</v>
+      </c>
+      <c r="E42" t="s">
+        <v>508</v>
+      </c>
+      <c r="F42" t="s">
+        <v>301</v>
+      </c>
+      <c r="G42" t="s">
+        <v>312</v>
+      </c>
+      <c r="H42" s="8">
+        <v>45106</v>
+      </c>
+      <c r="I42" t="s">
+        <v>315</v>
+      </c>
+      <c r="J42" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" t="s">
+        <v>268</v>
+      </c>
+      <c r="C43" t="s">
         <v>278</v>
       </c>
-      <c r="G39" s="8">
-        <v>45555</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B40" t="s">
-        <v>271</v>
-      </c>
-      <c r="C40" t="s">
-        <v>287</v>
-      </c>
-      <c r="G40" s="8">
-        <v>45798</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" t="s">
-        <v>272</v>
-      </c>
-      <c r="C41" t="s">
-        <v>283</v>
-      </c>
-      <c r="G41" s="8">
-        <v>45595</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A42" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B42" t="s">
-        <v>272</v>
-      </c>
-      <c r="C42" t="s">
-        <v>284</v>
-      </c>
-      <c r="G42" s="8">
-        <v>45106</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A43" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B43" t="s">
-        <v>271</v>
-      </c>
-      <c r="C43" t="s">
-        <v>281</v>
-      </c>
-      <c r="G43" s="8">
+      <c r="E43" t="s">
+        <v>507</v>
+      </c>
+      <c r="F43" t="s">
+        <v>299</v>
+      </c>
+      <c r="G43" t="s">
+        <v>312</v>
+      </c>
+      <c r="H43" s="8">
         <v>46117</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I43" t="s">
+        <v>315</v>
+      </c>
+      <c r="J43" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A44" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C44" t="s">
+        <v>277</v>
+      </c>
+      <c r="E44" t="s">
+        <v>506</v>
+      </c>
+      <c r="F44" t="s">
+        <v>504</v>
+      </c>
+      <c r="G44" t="s">
+        <v>312</v>
+      </c>
+      <c r="H44" s="8">
+        <v>45683</v>
+      </c>
+      <c r="I44" t="s">
+        <v>315</v>
+      </c>
+      <c r="J44" t="s">
+        <v>315</v>
+      </c>
+      <c r="M44" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>269</v>
+      </c>
+      <c r="C45" t="s">
         <v>280</v>
       </c>
-      <c r="G44" s="8">
-        <v>45683</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>272</v>
-      </c>
-      <c r="C45" t="s">
-        <v>283</v>
-      </c>
-      <c r="G45" s="8">
+      <c r="E45" t="s">
+        <v>304</v>
+      </c>
+      <c r="F45" t="s">
+        <v>301</v>
+      </c>
+      <c r="G45" t="s">
+        <v>312</v>
+      </c>
+      <c r="H45" s="8">
         <v>45007</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I45" t="s">
+        <v>315</v>
+      </c>
+      <c r="J45" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A46" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B46" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C46" t="s">
-        <v>285</v>
-      </c>
-      <c r="G46" s="8">
+        <v>282</v>
+      </c>
+      <c r="E46" t="s">
+        <v>308</v>
+      </c>
+      <c r="F46" t="s">
+        <v>504</v>
+      </c>
+      <c r="G46" t="s">
+        <v>313</v>
+      </c>
+      <c r="H46" s="8">
         <v>45335</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I46" t="s">
+        <v>315</v>
+      </c>
+      <c r="J46" t="s">
+        <v>315</v>
+      </c>
+      <c r="M46" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A47" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B47" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C47" t="s">
-        <v>278</v>
-      </c>
-      <c r="G47" s="8">
+        <v>275</v>
+      </c>
+      <c r="E47" t="s">
+        <v>305</v>
+      </c>
+      <c r="F47" t="s">
+        <v>298</v>
+      </c>
+      <c r="G47" t="s">
+        <v>312</v>
+      </c>
+      <c r="H47" s="8">
         <v>45099</v>
       </c>
+      <c r="I47" t="s">
+        <v>315</v>
+      </c>
+      <c r="J47" t="s">
+        <v>315</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K2" xr:uid="{CD7C3BF9-6E18-42C7-89A4-749286D4D001}"/>
+  <autoFilter ref="A2:M47" xr:uid="{DCD48263-85C3-46FB-BEDD-4C138BA22038}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2270,6 +4272,8 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
     <col min="7" max="7" width="19.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.125" bestFit="1" customWidth="1"/>
@@ -2280,7 +4284,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
@@ -2288,45 +4292,48 @@
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>92</v>
-      </c>
       <c r="K2" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C3" t="s">
+        <v>285</v>
       </c>
       <c r="G3" s="8">
         <v>45397</v>
@@ -2334,10 +4341,13 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C4" t="s">
+        <v>286</v>
       </c>
       <c r="G4" s="8">
         <v>46105</v>
@@ -2345,10 +4355,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C5" t="s">
+        <v>287</v>
       </c>
       <c r="G5" s="8">
         <v>45794</v>
@@ -2356,10 +4369,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C6" t="s">
+        <v>288</v>
       </c>
       <c r="G6" s="8">
         <v>45955</v>
@@ -2367,10 +4383,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C7" t="s">
+        <v>289</v>
       </c>
       <c r="G7" s="8">
         <v>45919</v>
@@ -2378,10 +4397,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C8" t="s">
+        <v>286</v>
       </c>
       <c r="G8" s="8">
         <v>45124</v>
@@ -2389,10 +4411,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C9" t="s">
+        <v>285</v>
       </c>
       <c r="G9" s="8">
         <v>45392</v>
@@ -2400,10 +4425,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C10" t="s">
+        <v>290</v>
       </c>
       <c r="G10" s="8">
         <v>44475</v>
@@ -2411,10 +4439,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C11" t="s">
+        <v>285</v>
       </c>
       <c r="G11" s="8">
         <v>45376</v>
@@ -2422,10 +4453,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C12" t="s">
+        <v>287</v>
       </c>
       <c r="G12" s="8">
         <v>44568</v>
@@ -2433,10 +4467,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C13" t="s">
+        <v>291</v>
       </c>
       <c r="G13" s="8">
         <v>45347</v>
@@ -2444,10 +4481,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C14" t="s">
+        <v>286</v>
       </c>
       <c r="G14" s="8">
         <v>46161</v>
@@ -2455,10 +4495,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C15" t="s">
+        <v>292</v>
       </c>
       <c r="G15" s="8">
         <v>45057</v>
@@ -2466,10 +4509,13 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>293</v>
       </c>
       <c r="G16" s="8">
         <v>44677</v>
@@ -2477,10 +4523,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C17" t="s">
+        <v>285</v>
       </c>
       <c r="G17" s="8">
         <v>46283</v>
@@ -2488,10 +4537,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C18" t="s">
+        <v>288</v>
       </c>
       <c r="G18" s="8">
         <v>45200</v>
@@ -2499,10 +4551,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C19" t="s">
+        <v>287</v>
       </c>
       <c r="G19" s="8">
         <v>44561</v>
@@ -2510,10 +4565,13 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C20" t="s">
+        <v>285</v>
       </c>
       <c r="G20" s="8">
         <v>45706</v>
@@ -2521,10 +4579,13 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C21" t="s">
+        <v>289</v>
       </c>
       <c r="G21" s="8">
         <v>44890</v>
@@ -2532,10 +4593,13 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C22" t="s">
+        <v>286</v>
       </c>
       <c r="G22" s="8">
         <v>44870</v>
@@ -2543,10 +4607,13 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C23" t="s">
+        <v>288</v>
       </c>
       <c r="G23" s="8">
         <v>46324</v>
@@ -2554,10 +4621,13 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C24" t="s">
+        <v>286</v>
       </c>
       <c r="G24" s="8">
         <v>45180</v>
@@ -2565,10 +4635,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B25" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C25" t="s">
+        <v>285</v>
       </c>
       <c r="G25" s="8">
         <v>45529</v>
@@ -2576,10 +4649,13 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C26" t="s">
+        <v>287</v>
       </c>
       <c r="G26" s="8">
         <v>45554</v>
@@ -2587,10 +4663,13 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B27" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C27" t="s">
+        <v>285</v>
       </c>
       <c r="G27" s="8">
         <v>45761</v>
@@ -2598,10 +4677,13 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C28" t="s">
+        <v>289</v>
       </c>
       <c r="G28" s="8">
         <v>44811</v>
@@ -2609,10 +4691,13 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C29" t="s">
+        <v>288</v>
       </c>
       <c r="G29" s="8">
         <v>46339</v>
@@ -2620,10 +4705,13 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C30" t="s">
+        <v>286</v>
       </c>
       <c r="G30" s="8">
         <v>44508</v>
@@ -2631,10 +4719,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C31" t="s">
+        <v>285</v>
       </c>
       <c r="G31" s="8">
         <v>46237</v>
@@ -2642,10 +4733,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C32" t="s">
+        <v>287</v>
       </c>
       <c r="G32" s="8">
         <v>44817</v>
@@ -2653,10 +4747,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C33" t="s">
+        <v>286</v>
       </c>
       <c r="G33" s="8">
         <v>44905</v>
@@ -2664,10 +4761,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C34" t="s">
+        <v>290</v>
       </c>
       <c r="G34" s="8">
         <v>45514</v>
@@ -2675,10 +4775,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C35" t="s">
+        <v>285</v>
       </c>
       <c r="G35" s="8">
         <v>44585</v>
@@ -2686,10 +4789,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C36" t="s">
+        <v>294</v>
       </c>
       <c r="G36" s="8">
         <v>45873</v>
@@ -2697,10 +4803,13 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C37" t="s">
+        <v>287</v>
       </c>
       <c r="G37" s="8">
         <v>44914</v>
@@ -2708,10 +4817,13 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B38" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C38" t="s">
+        <v>286</v>
       </c>
       <c r="G38" s="8">
         <v>44511</v>
@@ -2719,10 +4831,13 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B39" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C39" t="s">
+        <v>292</v>
       </c>
       <c r="G39" s="8">
         <v>43983</v>
@@ -2730,10 +4845,13 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B40" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C40" t="s">
+        <v>286</v>
       </c>
       <c r="G40" s="8">
         <v>43308</v>
@@ -2741,10 +4859,13 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B41" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="C41" t="s">
+        <v>290</v>
       </c>
       <c r="G41" s="8">
         <v>43789</v>
@@ -2752,10 +4873,16 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B42" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="C42" t="s">
+        <v>286</v>
+      </c>
+      <c r="E42" t="s">
+        <v>303</v>
       </c>
       <c r="G42" s="8">
         <v>43254</v>
@@ -2765,6 +4892,7 @@
   <autoFilter ref="A2:L2" xr:uid="{39242409-8D72-4F27-A96C-1558A95E4978}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2782,7 +4910,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
@@ -2790,651 +4918,651 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G6" s="10"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G14" s="10"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G15" s="10"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G16" s="10"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G17" s="10"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G19" s="10"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G20" s="10"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G21" s="10"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G22" s="10"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G23" s="10"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G30" s="10"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G32" s="10"/>
     </row>
@@ -3456,42 +5584,42 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D2" t="s">
         <v>260</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>261</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>262</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>263</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>264</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>265</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>266</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>267</v>
-      </c>
-      <c r="I2" t="s">
-        <v>268</v>
-      </c>
-      <c r="J2" t="s">
-        <v>269</v>
-      </c>
-      <c r="K2" t="s">
-        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -3507,7 +5635,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -3518,20 +5646,258 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DFF8774-4F9F-472E-8C7F-6D532CD8553F}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>253</v>
-      </c>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="F3" s="10">
+        <v>50</v>
+      </c>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="F4" s="10">
+        <v>40</v>
+      </c>
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="F5" s="10">
+        <v>30</v>
+      </c>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="F6" s="10">
+        <v>40</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="F7" s="10">
+        <v>50</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="F8" s="10">
+        <v>30</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="F9" s="10">
+        <v>30</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="F10" s="10">
+        <v>50</v>
+      </c>
+      <c r="G10" s="10"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="F11" s="10">
+        <v>40</v>
+      </c>
+      <c r="G11" s="10"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="F12" s="10">
+        <v>50</v>
+      </c>
+      <c r="G12" s="10"/>
     </row>
   </sheetData>
+  <autoFilter ref="A2:G12" xr:uid="{938E9866-BD6E-4A0C-A2A3-0075D3FD0104}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3540,13 +5906,656 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FB11BE6-8671-47EE-AC44-313417A4F7A6}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="22.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>259</v>
-      </c>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="J3" s="14"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A4" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="J4" s="14"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A5" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="J5" s="14"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A6" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A7" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="J7" s="14"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A8" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A9" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A10" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A11" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A12" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A13" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A14" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A15" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A16" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>466</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A17" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A18" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A19" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A20" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A21" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>494</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A22" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>502</v>
+      </c>
+      <c r="J22" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
